--- a/site/Any-Source-to-JIRA-Service-Management-Integration-Guide/headings.xlsx
+++ b/site/Any-Source-to-JIRA-Service-Management-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -473,19 +473,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01KRXHHNYZP8KY0GM1VQQMJCK1</t>
+          <t>h_01KRZ9RC0YQWD98B52263MYTQ2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXHHNYZP8KY0GM1VQQMJCK1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRZ9RC0YQWD98B52263MYTQ2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,41 +495,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01J46B7Y1FJFZ9EF69E21925AA</t>
+          <t>h_01KRXHHNYZP8KY0GM1VQQMJCK1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01J46B7Y1FJFZ9EF69E21925AA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXHHNYZP8KY0GM1VQQMJCK1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01KRJZGDHVK39XCQKBKZFD5519</t>
+          <t>h_01J46B7Y1FJFZ9EF69E21925AA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRJZGDHVK39XCQKBKZFD5519</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01J46B7Y1FJFZ9EF69E21925AA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Source Applicatio n</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,19 +539,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01KRXERB6990XCM5QE4QJ1GPKY</t>
+          <t>h_01KRZAH40ZXF6A2NBMSC7W79CJ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXERB6990XCM5QE4QJ1GPKY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRZAH40ZXF6A2NBMSC7W79CJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JIRA</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,85 +561,85 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01KRXCM2Q9HS02WVDV4QVHT6ZY</t>
+          <t>h_01KRJZGDHVK39XCQKBKZFD5519</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXCM2Q9HS02WVDV4QVHT6ZY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRJZGDHVK39XCQKBKZFD5519</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JIRA Settings</t>
+          <t>Source Application</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KRXD9V8WYRPQV719W926RNZJ</t>
+          <t>h_01KRXERB6990XCM5QE4QJ1GPKY</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXD9V8WYRPQV719W926RNZJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXERB6990XCM5QE4QJ1GPKY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ticket Generation</t>
+          <t>JIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KRXDBS3NB4X16RPFKK7T5WNB</t>
+          <t>h_01KRXCM2Q9HS02WVDV4QVHT6ZY</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXDBS3NB4X16RPFKK7T5WNB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXCM2Q9HS02WVDV4QVHT6ZY</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>JIRA Settings</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KRXA6AHVW8369XX6N26ZP5GS</t>
+          <t>h_01KRXD9V8WYRPQV719W926RNZJ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXA6AHVW8369XX6N26ZP5GS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXD9V8WYRPQV719W926RNZJ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Advanced settings</t>
+          <t>Ticket Generation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -649,85 +649,85 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KRX6396CQ8M4PG93MPCD108E</t>
+          <t>h_01KRXDBS3NB4X16RPFKK7T5WNB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX6396CQ8M4PG93MPCD108E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXDBS3NB4X16RPFKK7T5WNB</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KRX6EQP4NHSC44A9F21QFPXK</t>
+          <t>h_01KRXA6AHVW8369XX6N26ZP5GS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX6EQP4NHSC44A9F21QFPXK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRXA6AHVW8369XX6N26ZP5GS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Advanced settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KRX70G5CCBYMNSYTD4PZNG78</t>
+          <t>h_01KRX6396CQ8M4PG93MPCD108E</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX70G5CCBYMNSYTD4PZNG78</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX6396CQ8M4PG93MPCD108E</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KRX72TRZ4WQJ50AVN4N859X1</t>
+          <t>h_01KRX6EQP4NHSC44A9F21QFPXK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX72TRZ4WQJ50AVN4N859X1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX6EQP4NHSC44A9F21QFPXK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,54 +737,98 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KRX740JB1KH2H35Q1WVQ7HNP</t>
+          <t>h_01KRX70G5CCBYMNSYTD4PZNG78</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX740JB1KH2H35Q1WVQ7HNP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX70G5CCBYMNSYTD4PZNG78</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KRX8AY3P41TJTJ2BSD9RBWCV</t>
+          <t>h_01KRX72TRZ4WQJ50AVN4N859X1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX8AY3P41TJTJ2BSD9RBWCV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX72TRZ4WQJ50AVN4N859X1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KRX740JB1KH2H35Q1WVQ7HNP</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX740JB1KH2H35Q1WVQ7HNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KRX8AY3P41TJTJ2BSD9RBWCV</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KRX8AY3P41TJTJ2BSD9RBWCV</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Any-Source-to-JIRA-Service-Management-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
